--- a/public/templates/출력일보.xlsx
+++ b/public/templates/출력일보.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\서재형\Desktop\new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42455969-1A55-4842-A88D-3A604EA361D8}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA0030-057A-4238-9FD8-2BE58A94B09F}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7E9BC92A-A51C-4B42-921D-F03DA5080256}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7E9BC92A-A51C-4B42-921D-F03DA5080256}"/>
   </bookViews>
   <sheets>
     <sheet name="260701" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>출 력 일 보</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -106,51 +106,67 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>직영</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>단열</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>합지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>금일 출력 및 작업현황</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>위치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업내용</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹매김</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경량벽체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>세대천정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공용홀천정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>걸레받이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>수장</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>직영</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>걸레받이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>단열</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>경량</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>합지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>천정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>금일 출력 및 작업현황</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>성명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>위치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업내용</t>
+    <t>외주</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -888,32 +904,50 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -957,53 +991,35 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1338,22 +1354,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="72" t="s">
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="72"/>
+      <c r="J1" s="78"/>
       <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1362,90 +1378,90 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
     </row>
     <row r="3" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63" t="s">
+      <c r="B3" s="68"/>
+      <c r="C3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
     </row>
     <row r="4" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63" t="s">
+      <c r="B4" s="68"/>
+      <c r="C4" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
     </row>
     <row r="5" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66">
+      <c r="B5" s="71"/>
+      <c r="C5" s="72">
         <v>46204</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
     </row>
     <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="52" t="s">
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
     </row>
     <row r="7" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -1454,26 +1470,26 @@
       <c r="B7" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="57"/>
+      <c r="D7" s="82"/>
       <c r="E7" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="50" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="57"/>
+      <c r="J7" s="82"/>
       <c r="K7" s="46" t="s">
         <v>14</v>
       </c>
@@ -1488,30 +1504,30 @@
       <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="58">
-        <f>COUNTIF($B$18:$B$57,$B8)+COUNTIF($H$18:$H$57,$B8)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="58"/>
+      <c r="C8" s="83">
+        <f t="shared" ref="C8:C14" si="0">COUNTIF($B$18:$B$57,$B8)+COUNTIF($H$18:$H$57,$B8)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="83"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="80">
-        <f t="shared" ref="F8:F14" si="0">C8+E8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="74">
+      <c r="F8" s="56">
+        <f t="shared" ref="F8:F14" si="1">C8+E8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="51">
         <v>8</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="58">
-        <f>COUNTIF($B$18:$B$57,$H8)+COUNTIF($H$18:$H$57,$H8)</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="58"/>
+        <v>29</v>
+      </c>
+      <c r="I8" s="83">
+        <f t="shared" ref="I8:I14" si="2">COUNTIF($B$18:$B$57,$H8)+COUNTIF($H$18:$H$57,$H8)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="83"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8">
-        <f t="shared" ref="L8:L14" si="1">I8+K8</f>
+        <f t="shared" ref="L8:L14" si="3">I8+K8</f>
         <v>0</v>
       </c>
     </row>
@@ -1523,203 +1539,211 @@
       <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="53">
-        <f>COUNTIF($B$18:$B$57,$B9)+COUNTIF($H$18:$H$57,$B9)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="53"/>
+      <c r="C9" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D9" s="84"/>
       <c r="E9" s="12"/>
-      <c r="F9" s="81">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="75">
+      <c r="F9" s="57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="52">
         <f>G8+1</f>
         <v>9</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="53">
-        <f>COUNTIF($B$18:$B$57,$H9)+COUNTIF($H$18:$H$57,$H9)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="53"/>
+        <v>30</v>
+      </c>
+      <c r="I9" s="84">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="84"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
-        <f t="shared" ref="A10:A14" si="2">A9+1</f>
+        <f t="shared" ref="A10:A14" si="4">A9+1</f>
         <v>3</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="53">
-        <f>COUNTIF($B$18:$B$57,$B10)+COUNTIF($H$18:$H$57,$B10)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="53"/>
+        <v>19</v>
+      </c>
+      <c r="C10" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="84"/>
       <c r="E10" s="12"/>
-      <c r="F10" s="81">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="75">
-        <f t="shared" ref="G10:G14" si="3">G9+1</f>
+      <c r="F10" s="57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="52">
+        <f t="shared" ref="G10:G14" si="5">G9+1</f>
         <v>10</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="53">
-        <f>COUNTIF($B$18:$B$57,$H10)+COUNTIF($H$18:$H$57,$H10)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="53"/>
+        <v>17</v>
+      </c>
+      <c r="I10" s="84">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="84"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D11" s="84"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="52">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="84">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="53">
-        <f>COUNTIF($B$18:$B$57,$B11)+COUNTIF($H$18:$H$57,$B11)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="81">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="75">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="53">
-        <f>COUNTIF($B$18:$B$57,$H11)+COUNTIF($H$18:$H$57,$H11)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="84"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D12" s="84"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="52">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="84">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="53">
-        <f>COUNTIF($B$18:$B$57,$B12)+COUNTIF($H$18:$H$57,$B12)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="81">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="75">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="53">
-        <f>COUNTIF($B$18:$B$57,$H12)+COUNTIF($H$18:$H$57,$H12)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="84"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="87">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D13" s="87"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="53">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="87">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="54">
-        <f>COUNTIF($B$18:$B$57,$B13)+COUNTIF($H$18:$H$57,$B13)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="82">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="76">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="54">
-        <f>COUNTIF($B$18:$B$57,$H13)+COUNTIF($H$18:$H$57,$H13)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="54"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="87"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D14" s="88"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="54">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="88">
         <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="55">
-        <f>COUNTIF($B$18:$B$57,$B14)+COUNTIF($H$18:$H$57,$B14)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="83">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="77">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="55">
-        <f>COUNTIF($B$18:$B$57,$H14)+COUNTIF($H$18:$H$57,$H14)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="55"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="88"/>
       <c r="K14" s="23"/>
       <c r="L14" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1738,20 +1762,20 @@
       <c r="L15" s="27"/>
     </row>
     <row r="16" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="52"/>
+      <c r="A16" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="81"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48" t="s">
@@ -1761,16 +1785,16 @@
         <v>12</v>
       </c>
       <c r="C17" s="48" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>11</v>
@@ -1779,16 +1803,16 @@
         <v>12</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J17" s="48" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K17" s="48" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L17" s="48" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -1812,7 +1836,7 @@
     </row>
     <row r="19" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
-        <f t="shared" ref="A19:A31" si="4">A18+1</f>
+        <f t="shared" ref="A19:A31" si="6">A18+1</f>
         <v>2</v>
       </c>
       <c r="B19" s="32"/>
@@ -1832,7 +1856,7 @@
     </row>
     <row r="20" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="B20" s="32"/>
@@ -1841,7 +1865,7 @@
       <c r="E20" s="33"/>
       <c r="F20" s="33"/>
       <c r="G20" s="36">
-        <f t="shared" ref="G20:G46" si="5">G19+1</f>
+        <f t="shared" ref="G20:G46" si="7">G19+1</f>
         <v>43</v>
       </c>
       <c r="H20" s="32"/>
@@ -1852,7 +1876,7 @@
     </row>
     <row r="21" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="B21" s="32"/>
@@ -1861,7 +1885,7 @@
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
       <c r="G21" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="H21" s="32"/>
@@ -1872,7 +1896,7 @@
     </row>
     <row r="22" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="B22" s="32"/>
@@ -1881,7 +1905,7 @@
       <c r="E22" s="33"/>
       <c r="F22" s="34"/>
       <c r="G22" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>45</v>
       </c>
       <c r="H22" s="32"/>
@@ -1892,7 +1916,7 @@
     </row>
     <row r="23" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="B23" s="32"/>
@@ -1901,7 +1925,7 @@
       <c r="E23" s="33"/>
       <c r="F23" s="34"/>
       <c r="G23" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>46</v>
       </c>
       <c r="H23" s="32"/>
@@ -1912,7 +1936,7 @@
     </row>
     <row r="24" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="B24" s="32"/>
@@ -1921,7 +1945,7 @@
       <c r="E24" s="33"/>
       <c r="F24" s="34"/>
       <c r="G24" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>47</v>
       </c>
       <c r="H24" s="32"/>
@@ -1932,7 +1956,7 @@
     </row>
     <row r="25" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="B25" s="32"/>
@@ -1941,7 +1965,7 @@
       <c r="E25" s="33"/>
       <c r="F25" s="34"/>
       <c r="G25" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>48</v>
       </c>
       <c r="H25" s="32"/>
@@ -1952,7 +1976,7 @@
     </row>
     <row r="26" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="B26" s="32"/>
@@ -1961,7 +1985,7 @@
       <c r="E26" s="33"/>
       <c r="F26" s="34"/>
       <c r="G26" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="H26" s="32"/>
@@ -1972,7 +1996,7 @@
     </row>
     <row r="27" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="B27" s="32"/>
@@ -1981,7 +2005,7 @@
       <c r="E27" s="33"/>
       <c r="F27" s="37"/>
       <c r="G27" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="H27" s="32"/>
@@ -1992,7 +2016,7 @@
     </row>
     <row r="28" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="B28" s="32"/>
@@ -2001,7 +2025,7 @@
       <c r="E28" s="38"/>
       <c r="F28" s="37"/>
       <c r="G28" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>51</v>
       </c>
       <c r="H28" s="32"/>
@@ -2012,7 +2036,7 @@
     </row>
     <row r="29" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="B29" s="39"/>
@@ -2021,7 +2045,7 @@
       <c r="E29" s="38"/>
       <c r="F29" s="40"/>
       <c r="G29" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>52</v>
       </c>
       <c r="H29" s="32"/>
@@ -2032,7 +2056,7 @@
     </row>
     <row r="30" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="B30" s="32"/>
@@ -2041,7 +2065,7 @@
       <c r="E30" s="38"/>
       <c r="F30" s="37"/>
       <c r="G30" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>53</v>
       </c>
       <c r="H30" s="32"/>
@@ -2052,7 +2076,7 @@
     </row>
     <row r="31" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="B31" s="39"/>
@@ -2061,7 +2085,7 @@
       <c r="E31" s="38"/>
       <c r="F31" s="41"/>
       <c r="G31" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>54</v>
       </c>
       <c r="H31" s="32"/>
@@ -2081,7 +2105,7 @@
       <c r="E32" s="33"/>
       <c r="F32" s="37"/>
       <c r="G32" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>55</v>
       </c>
       <c r="H32" s="32"/>
@@ -2092,7 +2116,7 @@
     </row>
     <row r="33" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
-        <f t="shared" ref="A33:A46" si="6">A32+1</f>
+        <f t="shared" ref="A33:A46" si="8">A32+1</f>
         <v>16</v>
       </c>
       <c r="B33" s="32"/>
@@ -2101,7 +2125,7 @@
       <c r="E33" s="33"/>
       <c r="F33" s="37"/>
       <c r="G33" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>56</v>
       </c>
       <c r="H33" s="32"/>
@@ -2112,7 +2136,7 @@
     </row>
     <row r="34" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="B34" s="32"/>
@@ -2121,7 +2145,7 @@
       <c r="E34" s="33"/>
       <c r="F34" s="33"/>
       <c r="G34" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>57</v>
       </c>
       <c r="H34" s="32"/>
@@ -2132,7 +2156,7 @@
     </row>
     <row r="35" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="B35" s="32"/>
@@ -2141,7 +2165,7 @@
       <c r="E35" s="33"/>
       <c r="F35" s="33"/>
       <c r="G35" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>58</v>
       </c>
       <c r="H35" s="32"/>
@@ -2152,7 +2176,7 @@
     </row>
     <row r="36" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="B36" s="32"/>
@@ -2161,7 +2185,7 @@
       <c r="E36" s="33"/>
       <c r="F36" s="34"/>
       <c r="G36" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>59</v>
       </c>
       <c r="H36" s="39"/>
@@ -2172,7 +2196,7 @@
     </row>
     <row r="37" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="B37" s="32"/>
@@ -2181,7 +2205,7 @@
       <c r="E37" s="33"/>
       <c r="F37" s="34"/>
       <c r="G37" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="H37" s="32"/>
@@ -2192,7 +2216,7 @@
     </row>
     <row r="38" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="B38" s="39"/>
@@ -2201,7 +2225,7 @@
       <c r="E38" s="33"/>
       <c r="F38" s="41"/>
       <c r="G38" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>61</v>
       </c>
       <c r="H38" s="32"/>
@@ -2212,7 +2236,7 @@
     </row>
     <row r="39" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="B39" s="32"/>
@@ -2221,7 +2245,7 @@
       <c r="E39" s="33"/>
       <c r="F39" s="37"/>
       <c r="G39" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>62</v>
       </c>
       <c r="H39" s="32"/>
@@ -2232,7 +2256,7 @@
     </row>
     <row r="40" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="B40" s="32"/>
@@ -2241,7 +2265,7 @@
       <c r="E40" s="33"/>
       <c r="F40" s="37"/>
       <c r="G40" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="H40" s="42"/>
@@ -2252,7 +2276,7 @@
     </row>
     <row r="41" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="B41" s="32"/>
@@ -2261,7 +2285,7 @@
       <c r="E41" s="33"/>
       <c r="F41" s="37"/>
       <c r="G41" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>64</v>
       </c>
       <c r="H41" s="42"/>
@@ -2272,7 +2296,7 @@
     </row>
     <row r="42" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="B42" s="32"/>
@@ -2281,7 +2305,7 @@
       <c r="E42" s="33"/>
       <c r="F42" s="33"/>
       <c r="G42" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>65</v>
       </c>
       <c r="H42" s="42"/>
@@ -2292,7 +2316,7 @@
     </row>
     <row r="43" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="B43" s="32"/>
@@ -2301,7 +2325,7 @@
       <c r="E43" s="33"/>
       <c r="F43" s="33"/>
       <c r="G43" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>66</v>
       </c>
       <c r="H43" s="42"/>
@@ -2312,7 +2336,7 @@
     </row>
     <row r="44" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="B44" s="32"/>
@@ -2321,7 +2345,7 @@
       <c r="E44" s="33"/>
       <c r="F44" s="33"/>
       <c r="G44" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>67</v>
       </c>
       <c r="H44" s="42"/>
@@ -2332,7 +2356,7 @@
     </row>
     <row r="45" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="B45" s="32"/>
@@ -2341,7 +2365,7 @@
       <c r="E45" s="33"/>
       <c r="F45" s="33"/>
       <c r="G45" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>68</v>
       </c>
       <c r="H45" s="42"/>
@@ -2352,7 +2376,7 @@
     </row>
     <row r="46" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>29</v>
       </c>
       <c r="B46" s="32"/>
@@ -2361,7 +2385,7 @@
       <c r="E46" s="33"/>
       <c r="F46" s="33"/>
       <c r="G46" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>69</v>
       </c>
       <c r="H46" s="42"/>
@@ -2371,7 +2395,7 @@
       <c r="L46" s="44"/>
     </row>
     <row r="47" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="84">
+      <c r="A47" s="60">
         <f>A46+1</f>
         <v>30</v>
       </c>
@@ -2380,19 +2404,19 @@
       <c r="D47" s="39"/>
       <c r="E47" s="38"/>
       <c r="F47" s="38"/>
-      <c r="G47" s="85">
+      <c r="G47" s="61">
         <f>G46+1</f>
         <v>70</v>
       </c>
-      <c r="H47" s="86"/>
-      <c r="I47" s="86"/>
-      <c r="J47" s="86"/>
-      <c r="K47" s="87"/>
-      <c r="L47" s="88"/>
+      <c r="H47" s="62"/>
+      <c r="I47" s="62"/>
+      <c r="J47" s="62"/>
+      <c r="K47" s="63"/>
+      <c r="L47" s="64"/>
     </row>
     <row r="48" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="84">
-        <f t="shared" ref="A48:A57" si="7">A47+1</f>
+      <c r="A48" s="60">
+        <f t="shared" ref="A48:A57" si="9">A47+1</f>
         <v>31</v>
       </c>
       <c r="B48" s="39"/>
@@ -2400,19 +2424,19 @@
       <c r="D48" s="39"/>
       <c r="E48" s="38"/>
       <c r="F48" s="38"/>
-      <c r="G48" s="85">
-        <f t="shared" ref="G48:G57" si="8">G47+1</f>
+      <c r="G48" s="61">
+        <f t="shared" ref="G48:G57" si="10">G47+1</f>
         <v>71</v>
       </c>
-      <c r="H48" s="86"/>
-      <c r="I48" s="86"/>
-      <c r="J48" s="86"/>
-      <c r="K48" s="87"/>
-      <c r="L48" s="88"/>
+      <c r="H48" s="62"/>
+      <c r="I48" s="62"/>
+      <c r="J48" s="62"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="64"/>
     </row>
     <row r="49" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="84">
-        <f t="shared" si="7"/>
+      <c r="A49" s="60">
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="B49" s="39"/>
@@ -2420,19 +2444,19 @@
       <c r="D49" s="39"/>
       <c r="E49" s="38"/>
       <c r="F49" s="38"/>
-      <c r="G49" s="85">
-        <f t="shared" si="8"/>
+      <c r="G49" s="61">
+        <f t="shared" si="10"/>
         <v>72</v>
       </c>
-      <c r="H49" s="86"/>
-      <c r="I49" s="86"/>
-      <c r="J49" s="86"/>
-      <c r="K49" s="87"/>
-      <c r="L49" s="88"/>
+      <c r="H49" s="62"/>
+      <c r="I49" s="62"/>
+      <c r="J49" s="62"/>
+      <c r="K49" s="63"/>
+      <c r="L49" s="64"/>
     </row>
     <row r="50" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="84">
-        <f t="shared" si="7"/>
+      <c r="A50" s="60">
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="B50" s="39"/>
@@ -2440,19 +2464,19 @@
       <c r="D50" s="39"/>
       <c r="E50" s="38"/>
       <c r="F50" s="38"/>
-      <c r="G50" s="85">
-        <f t="shared" si="8"/>
+      <c r="G50" s="61">
+        <f t="shared" si="10"/>
         <v>73</v>
       </c>
-      <c r="H50" s="86"/>
-      <c r="I50" s="86"/>
-      <c r="J50" s="86"/>
-      <c r="K50" s="87"/>
-      <c r="L50" s="88"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
+      <c r="J50" s="62"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="64"/>
     </row>
     <row r="51" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="84">
-        <f t="shared" si="7"/>
+      <c r="A51" s="60">
+        <f t="shared" si="9"/>
         <v>34</v>
       </c>
       <c r="B51" s="39"/>
@@ -2460,19 +2484,19 @@
       <c r="D51" s="39"/>
       <c r="E51" s="38"/>
       <c r="F51" s="38"/>
-      <c r="G51" s="85">
-        <f t="shared" si="8"/>
+      <c r="G51" s="61">
+        <f t="shared" si="10"/>
         <v>74</v>
       </c>
-      <c r="H51" s="86"/>
-      <c r="I51" s="86"/>
-      <c r="J51" s="86"/>
-      <c r="K51" s="87"/>
-      <c r="L51" s="88"/>
+      <c r="H51" s="62"/>
+      <c r="I51" s="62"/>
+      <c r="J51" s="62"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="64"/>
     </row>
     <row r="52" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="84">
-        <f t="shared" si="7"/>
+      <c r="A52" s="60">
+        <f t="shared" si="9"/>
         <v>35</v>
       </c>
       <c r="B52" s="39"/>
@@ -2480,19 +2504,19 @@
       <c r="D52" s="39"/>
       <c r="E52" s="38"/>
       <c r="F52" s="38"/>
-      <c r="G52" s="85">
-        <f t="shared" si="8"/>
+      <c r="G52" s="61">
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
-      <c r="H52" s="86"/>
-      <c r="I52" s="86"/>
-      <c r="J52" s="86"/>
-      <c r="K52" s="87"/>
-      <c r="L52" s="88"/>
+      <c r="H52" s="62"/>
+      <c r="I52" s="62"/>
+      <c r="J52" s="62"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="64"/>
     </row>
     <row r="53" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="84">
-        <f t="shared" si="7"/>
+      <c r="A53" s="60">
+        <f t="shared" si="9"/>
         <v>36</v>
       </c>
       <c r="B53" s="39"/>
@@ -2500,19 +2524,19 @@
       <c r="D53" s="39"/>
       <c r="E53" s="38"/>
       <c r="F53" s="38"/>
-      <c r="G53" s="85">
-        <f t="shared" si="8"/>
+      <c r="G53" s="61">
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
-      <c r="H53" s="86"/>
-      <c r="I53" s="86"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="87"/>
-      <c r="L53" s="88"/>
+      <c r="H53" s="62"/>
+      <c r="I53" s="62"/>
+      <c r="J53" s="62"/>
+      <c r="K53" s="63"/>
+      <c r="L53" s="64"/>
     </row>
     <row r="54" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="84">
-        <f t="shared" si="7"/>
+      <c r="A54" s="60">
+        <f t="shared" si="9"/>
         <v>37</v>
       </c>
       <c r="B54" s="39"/>
@@ -2520,19 +2544,19 @@
       <c r="D54" s="39"/>
       <c r="E54" s="38"/>
       <c r="F54" s="38"/>
-      <c r="G54" s="85">
-        <f t="shared" si="8"/>
+      <c r="G54" s="61">
+        <f t="shared" si="10"/>
         <v>77</v>
       </c>
-      <c r="H54" s="86"/>
-      <c r="I54" s="86"/>
-      <c r="J54" s="86"/>
-      <c r="K54" s="87"/>
-      <c r="L54" s="88"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="62"/>
+      <c r="J54" s="62"/>
+      <c r="K54" s="63"/>
+      <c r="L54" s="64"/>
     </row>
     <row r="55" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="84">
-        <f t="shared" si="7"/>
+      <c r="A55" s="60">
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="B55" s="39"/>
@@ -2540,19 +2564,19 @@
       <c r="D55" s="39"/>
       <c r="E55" s="38"/>
       <c r="F55" s="38"/>
-      <c r="G55" s="85">
-        <f t="shared" si="8"/>
+      <c r="G55" s="61">
+        <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="H55" s="86"/>
-      <c r="I55" s="86"/>
-      <c r="J55" s="86"/>
-      <c r="K55" s="87"/>
-      <c r="L55" s="88"/>
+      <c r="H55" s="62"/>
+      <c r="I55" s="62"/>
+      <c r="J55" s="62"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="64"/>
     </row>
     <row r="56" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="84">
-        <f t="shared" si="7"/>
+      <c r="A56" s="60">
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="B56" s="39"/>
@@ -2560,19 +2584,19 @@
       <c r="D56" s="39"/>
       <c r="E56" s="38"/>
       <c r="F56" s="38"/>
-      <c r="G56" s="85">
-        <f t="shared" si="8"/>
+      <c r="G56" s="61">
+        <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="H56" s="86"/>
-      <c r="I56" s="86"/>
-      <c r="J56" s="86"/>
-      <c r="K56" s="87"/>
-      <c r="L56" s="88"/>
+      <c r="H56" s="62"/>
+      <c r="I56" s="62"/>
+      <c r="J56" s="62"/>
+      <c r="K56" s="63"/>
+      <c r="L56" s="64"/>
     </row>
     <row r="57" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="84">
-        <f t="shared" si="7"/>
+      <c r="A57" s="60">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="B57" s="39"/>
@@ -2580,15 +2604,15 @@
       <c r="D57" s="39"/>
       <c r="E57" s="38"/>
       <c r="F57" s="38"/>
-      <c r="G57" s="85">
-        <f t="shared" si="8"/>
+      <c r="G57" s="61">
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
-      <c r="H57" s="86"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="87"/>
-      <c r="L57" s="88"/>
+      <c r="H57" s="62"/>
+      <c r="I57" s="62"/>
+      <c r="J57" s="62"/>
+      <c r="K57" s="63"/>
+      <c r="L57" s="64"/>
     </row>
     <row r="58" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="45"/>
@@ -2685,6 +2709,25 @@
     <row r="85" ht="20.45" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="L2:L5"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:F3"/>
@@ -2698,25 +2741,6 @@
     <mergeCell ref="G2:H5"/>
     <mergeCell ref="I2:J5"/>
     <mergeCell ref="K2:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I14:J14"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/public/templates/출력일보.xlsx
+++ b/public/templates/출력일보.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\서재형\Desktop\new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA0030-057A-4238-9FD8-2BE58A94B09F}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AB1954-DAA5-466A-96B2-3522904C885F}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7E9BC92A-A51C-4B42-921D-F03DA5080256}"/>
   </bookViews>
   <sheets>
-    <sheet name="260701" sheetId="1" r:id="rId1"/>
+    <sheet name="출력일보" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'260701'!$A$1:$L$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">출력일보!$A$1:$L$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -949,6 +949,36 @@
     <xf numFmtId="41" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -990,36 +1020,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1354,22 +1354,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="78" t="s">
+      <c r="A1" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78" t="s">
+      <c r="H1" s="88"/>
+      <c r="I1" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="78"/>
+      <c r="J1" s="88"/>
       <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1378,90 +1378,90 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
     </row>
     <row r="3" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69" t="s">
+      <c r="B3" s="78"/>
+      <c r="C3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
     </row>
     <row r="4" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="69" t="s">
+      <c r="B4" s="78"/>
+      <c r="C4" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
     </row>
     <row r="5" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72">
+      <c r="B5" s="81"/>
+      <c r="C5" s="82">
         <v>46204</v>
       </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
     </row>
     <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="81" t="s">
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -1470,10 +1470,10 @@
       <c r="B7" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="82"/>
+      <c r="D7" s="73"/>
       <c r="E7" s="47" t="s">
         <v>14</v>
       </c>
@@ -1486,10 +1486,10 @@
       <c r="H7" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="82" t="s">
+      <c r="I7" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="82"/>
+      <c r="J7" s="73"/>
       <c r="K7" s="46" t="s">
         <v>14</v>
       </c>
@@ -1504,11 +1504,11 @@
       <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="74">
         <f t="shared" ref="C8:C14" si="0">COUNTIF($B$18:$B$57,$B8)+COUNTIF($H$18:$H$57,$B8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="83"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="7"/>
       <c r="F8" s="56">
         <f t="shared" ref="F8:F14" si="1">C8+E8</f>
@@ -1520,11 +1520,11 @@
       <c r="H8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="74">
         <f t="shared" ref="I8:I14" si="2">COUNTIF($B$18:$B$57,$H8)+COUNTIF($H$18:$H$57,$H8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="83"/>
+      <c r="J8" s="74"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8">
         <f t="shared" ref="L8:L14" si="3">I8+K8</f>
@@ -1539,11 +1539,11 @@
       <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="84">
+      <c r="C9" s="68">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9" s="84"/>
+      <c r="D9" s="68"/>
       <c r="E9" s="12"/>
       <c r="F9" s="57">
         <f t="shared" si="1"/>
@@ -1556,11 +1556,11 @@
       <c r="H9" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="84">
+      <c r="I9" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="84"/>
+      <c r="J9" s="68"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13">
         <f t="shared" si="3"/>
@@ -1575,11 +1575,11 @@
       <c r="B10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="84">
+      <c r="C10" s="68">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10" s="84"/>
+      <c r="D10" s="68"/>
       <c r="E10" s="12"/>
       <c r="F10" s="57">
         <f t="shared" si="1"/>
@@ -1592,11 +1592,11 @@
       <c r="H10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="84">
+      <c r="I10" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J10" s="84"/>
+      <c r="J10" s="68"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13">
         <f t="shared" si="3"/>
@@ -1611,11 +1611,11 @@
       <c r="B11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="84">
+      <c r="C11" s="68">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D11" s="84"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="12"/>
       <c r="F11" s="57">
         <f t="shared" si="1"/>
@@ -1628,11 +1628,11 @@
       <c r="H11" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="84">
+      <c r="I11" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J11" s="84"/>
+      <c r="J11" s="68"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13">
         <f t="shared" si="3"/>
@@ -1647,11 +1647,11 @@
       <c r="B12" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="84">
+      <c r="C12" s="68">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D12" s="84"/>
+      <c r="D12" s="68"/>
       <c r="E12" s="12"/>
       <c r="F12" s="57">
         <f t="shared" si="1"/>
@@ -1664,11 +1664,11 @@
       <c r="H12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="84">
+      <c r="I12" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J12" s="84"/>
+      <c r="J12" s="68"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13">
         <f t="shared" si="3"/>
@@ -1683,11 +1683,11 @@
       <c r="B13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="87">
+      <c r="C13" s="69">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D13" s="87"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="17"/>
       <c r="F13" s="58">
         <f t="shared" si="1"/>
@@ -1700,11 +1700,11 @@
       <c r="H13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="87">
+      <c r="I13" s="69">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J13" s="87"/>
+      <c r="J13" s="69"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18">
         <f t="shared" si="3"/>
@@ -1719,11 +1719,11 @@
       <c r="B14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="88">
+      <c r="C14" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14" s="88"/>
+      <c r="D14" s="70"/>
       <c r="E14" s="22"/>
       <c r="F14" s="59">
         <f t="shared" si="1"/>
@@ -1736,11 +1736,11 @@
       <c r="H14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="88">
+      <c r="I14" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J14" s="88"/>
+      <c r="J14" s="70"/>
       <c r="K14" s="23"/>
       <c r="L14" s="23">
         <f t="shared" si="3"/>
@@ -1762,20 +1762,20 @@
       <c r="L15" s="27"/>
     </row>
     <row r="16" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="85" t="s">
+      <c r="A16" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="81"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="67"/>
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48" t="s">
@@ -2709,25 +2709,6 @@
     <row r="85" ht="20.45" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="I8:J8"/>
     <mergeCell ref="L2:L5"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:F3"/>
@@ -2741,6 +2722,25 @@
     <mergeCell ref="G2:H5"/>
     <mergeCell ref="I2:J5"/>
     <mergeCell ref="K2:K5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I14:J14"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
